--- a/output/pdf_financials_xlsx/TTO.H.xlsx
+++ b/output/pdf_financials_xlsx/TTO.H.xlsx
@@ -5100,43 +5100,43 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.037301</v>
       </c>
     </row>
     <row r="93">
@@ -7784,7 +7784,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -8438,7 +8442,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10006,7 +10014,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11284,7 +11296,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -11878,7 +11894,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TTO.H.xlsx
+++ b/output/pdf_financials_xlsx/TTO.H.xlsx
@@ -2105,46 +2105,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09524199999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.151813</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.028556</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.00493</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001098</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.203789</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.147542</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.043707</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.018133</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.190035</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.163447</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.153437</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.11968</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.06497699999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2203,46 +2203,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09524199999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.151813</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.028556</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.00493</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001098</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.203789</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.147542</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.043707</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.018133</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.190035</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.163447</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.153437</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.11968</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.06497699999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.09524199999999999</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.151813</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.028556</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -22102,7 +22102,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">

--- a/output/pdf_financials_xlsx/TTO.H.xlsx
+++ b/output/pdf_financials_xlsx/TTO.H.xlsx
@@ -3803,37 +3803,37 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.008259000000000001</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.011056</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="68">
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00085</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00085</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -7237,7 +7237,7 @@
         <v>-0.024758</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.177478</v>
+        <v>-0.178328</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -13494,7 +13494,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -16412,7 +16416,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
